--- a/input/Studies/C3/C3_Prototypical_Sites/P5_3stages_nogaslift.xlsx
+++ b/input/Studies/C3/C3_Prototypical_Sites/P5_3stages_nogaslift.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmollel\Documents\MEET2\input\Studies\C3\C3_Prototypical_Sites\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmollel\Documents\MAES\input\Studies\C3\C3_Prototypical_Sites\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FC0338-9E2F-4626-83BA-32DCE38F0AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6003CD47-8C2E-4159-A7DD-A2A1F318813B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="925" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -1601,7 +1601,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">

--- a/input/Studies/C3/C3_Prototypical_Sites/P5_3stages_nogaslift.xlsx
+++ b/input/Studies/C3/C3_Prototypical_Sites/P5_3stages_nogaslift.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmollel\Documents\MAES\input\Studies\C3\C3_Prototypical_Sites\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MAES2\input\Studies\C3\C3_Prototypical_Sites\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6003CD47-8C2E-4159-A7DD-A2A1F318813B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB7C9A5-C6A8-4345-99A3-89985D418CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="925" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3337" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="296">
   <si>
     <t>Simulation Start Date</t>
   </si>
@@ -912,13 +912,31 @@
   </si>
   <si>
     <t>Max Downstream Equipment Capacity [scfh]</t>
+  </si>
+  <si>
+    <t>Actuator Type [Gas, Air, Electric, Mechanistic Gas]</t>
+  </si>
+  <si>
+    <t>Tank Controlled [True, False]</t>
+  </si>
+  <si>
+    <t>Well-Condensate.Stage1-Condensate.Stage2-Condensate.Tank-Flash</t>
+  </si>
+  <si>
+    <t>Crankcase Emissions Flag [TRUE, FALSE]</t>
+  </si>
+  <si>
+    <t>CCEE Ratio Distribution</t>
+  </si>
+  <si>
+    <t>Common/CrankcaseDistributions/crankcaseTest.csv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -960,8 +978,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1045,6 +1068,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -1124,7 +1153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1277,6 +1306,16 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1609,7 +1648,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7119,12 +7158,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -7158,297 +7197,306 @@
     <col min="37" max="37" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="13" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>100</v>
-      </c>
       <c r="D1" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="F1" s="52" t="s">
         <v>230</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="J1" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="J1" s="53" t="s">
+      <c r="K1" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="K1" s="53" t="s">
+      <c r="L1" s="53" t="s">
         <v>271</v>
       </c>
-      <c r="L1" s="36" t="s">
+      <c r="M1" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="M1" s="36" t="s">
+      <c r="N1" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="N1" s="36" t="s">
+      <c r="O1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="54" t="s">
+      <c r="P1" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="54" t="s">
+      <c r="Q1" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="Q1" s="54" t="s">
+      <c r="R1" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="36" t="s">
+      <c r="S1" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="S1" s="36" t="s">
+      <c r="T1" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="T1" s="36" t="s">
+      <c r="U1" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="U1" s="54" t="s">
+      <c r="V1" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="V1" s="54" t="s">
+      <c r="W1" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="W1" s="54" t="s">
+      <c r="X1" s="54" t="s">
         <v>277</v>
       </c>
-      <c r="X1" s="25" t="s">
+      <c r="Y1" s="25" t="s">
         <v>284</v>
       </c>
-      <c r="Y1" s="25" t="s">
+      <c r="Z1" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="Z1" s="25" t="s">
+      <c r="AA1" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="AA1" s="25" t="s">
+      <c r="AB1" s="25" t="s">
         <v>287</v>
       </c>
-      <c r="AB1" s="25" t="s">
+      <c r="AC1" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="AC1" s="25" t="s">
+      <c r="AD1" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="AD1" s="12" t="s">
+      <c r="AE1" s="61" t="s">
+        <v>291</v>
+      </c>
+      <c r="AF1" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AG1" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="9">
+        <v>2</v>
+      </c>
+      <c r="H2" s="9">
+        <v>365</v>
+      </c>
+      <c r="I2" s="9">
+        <v>4.3276E-3</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="49">
+        <v>0</v>
+      </c>
+      <c r="N2" s="49">
+        <v>365</v>
+      </c>
+      <c r="O2" s="49">
+        <v>0.34166999999999997</v>
+      </c>
+      <c r="P2" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="55">
+        <v>365</v>
+      </c>
+      <c r="R2" s="55">
+        <v>0.14960999999999999</v>
+      </c>
+      <c r="S2" s="49">
+        <v>3</v>
+      </c>
+      <c r="T2" s="49">
         <v>7</v>
       </c>
-      <c r="AE1" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="AF1" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="9">
-        <v>50</v>
-      </c>
-      <c r="G2" s="9">
-        <v>365</v>
-      </c>
-      <c r="H2" s="9">
-        <v>4.3276E-3</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="49">
-        <v>0</v>
-      </c>
-      <c r="M2" s="49">
-        <v>365</v>
-      </c>
-      <c r="N2" s="49">
+      <c r="U2" s="49">
         <v>0.34166999999999997</v>
-      </c>
-      <c r="O2" s="55">
-        <v>0</v>
-      </c>
-      <c r="P2" s="55">
-        <v>365</v>
-      </c>
-      <c r="Q2" s="55">
-        <v>0.14960999999999999</v>
-      </c>
-      <c r="R2" s="49">
-        <v>3</v>
-      </c>
-      <c r="S2" s="49">
-        <v>7</v>
-      </c>
-      <c r="T2" s="49">
-        <v>0.34166999999999997</v>
-      </c>
-      <c r="U2" s="55">
-        <v>7</v>
       </c>
       <c r="V2" s="55">
         <v>7</v>
       </c>
       <c r="W2" s="55">
+        <v>7</v>
+      </c>
+      <c r="X2" s="55">
         <v>0.14960999999999999</v>
       </c>
-      <c r="X2" s="26">
-        <v>1</v>
-      </c>
       <c r="Y2" s="26">
+        <v>5</v>
+      </c>
+      <c r="Z2" s="26">
+        <v>7</v>
+      </c>
+      <c r="AA2" s="26">
+        <v>1E-3</v>
+      </c>
+      <c r="AB2" s="56">
+        <v>3000</v>
+      </c>
+      <c r="AC2" s="56">
+        <v>6000</v>
+      </c>
+      <c r="AD2" s="56">
+        <v>5000</v>
+      </c>
+      <c r="AE2" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="9">
         <v>2</v>
       </c>
-      <c r="Z2" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="AA2" s="56">
-        <v>3000</v>
-      </c>
-      <c r="AB2" s="56">
-        <v>10000</v>
-      </c>
-      <c r="AC2" s="56">
-        <v>5000</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>264</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="9">
-        <v>50</v>
-      </c>
-      <c r="G3" s="9">
+      <c r="H3" s="9">
         <v>365</v>
       </c>
-      <c r="H3" s="9">
+      <c r="I3" s="9">
         <v>4.3276E-3</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>9</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="49">
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="49">
         <v>0</v>
       </c>
-      <c r="M3" s="49">
+      <c r="N3" s="49">
         <v>365</v>
       </c>
-      <c r="N3" s="49">
+      <c r="O3" s="49">
         <v>0.34166999999999997</v>
       </c>
-      <c r="O3" s="55">
+      <c r="P3" s="55">
         <v>0</v>
       </c>
-      <c r="P3" s="55">
+      <c r="Q3" s="55">
         <v>365</v>
       </c>
-      <c r="Q3" s="55">
+      <c r="R3" s="55">
         <v>0.14960999999999999</v>
       </c>
-      <c r="R3" s="49">
+      <c r="S3" s="49">
         <v>3</v>
       </c>
-      <c r="S3" s="49">
+      <c r="T3" s="49">
         <v>7</v>
       </c>
-      <c r="T3" s="49">
+      <c r="U3" s="49">
         <v>0.34166999999999997</v>
-      </c>
-      <c r="U3" s="55">
-        <v>7</v>
       </c>
       <c r="V3" s="55">
         <v>7</v>
       </c>
       <c r="W3" s="55">
+        <v>7</v>
+      </c>
+      <c r="X3" s="55">
         <v>0.14960999999999999</v>
       </c>
-      <c r="X3" s="26">
-        <v>1</v>
-      </c>
       <c r="Y3" s="26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z3" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="AA3" s="56">
+        <v>7</v>
+      </c>
+      <c r="AA3" s="26">
+        <v>1E-3</v>
+      </c>
+      <c r="AB3" s="56">
         <v>3000</v>
       </c>
-      <c r="AB3" s="56">
-        <v>10000</v>
-      </c>
       <c r="AC3" s="56">
+        <v>6000</v>
+      </c>
+      <c r="AD3" s="56">
         <v>5000</v>
       </c>
-      <c r="AD3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>265</v>
+      <c r="AE3" s="62" t="b">
+        <v>1</v>
       </c>
       <c r="AF3" t="s">
+        <v>292</v>
+      </c>
+      <c r="AG3" t="s">
         <v>263</v>
       </c>
     </row>
@@ -7460,546 +7508,564 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:BB3"/>
+  <dimension ref="A1:BD3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="15" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="10" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="15" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16" bestFit="1" customWidth="1"/>
+    <col min="54" max="55" width="65.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="21" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:56" s="21" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="63" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1" s="64" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="H1" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="I1" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="K1" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="M1" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="N1" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="P1" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="Q1" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="28" t="s">
+      <c r="R1" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="S1" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="T1" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="U1" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="V1" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="U1" s="31" t="s">
+      <c r="W1" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="V1" s="25" t="s">
+      <c r="X1" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="W1" s="25" t="s">
+      <c r="Y1" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="Z1" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="AA1" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="Z1" s="32" t="s">
+      <c r="AB1" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="AA1" s="33" t="s">
+      <c r="AC1" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="AB1" s="33" t="s">
+      <c r="AD1" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="AC1" s="33" t="s">
+      <c r="AE1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="12" t="s">
+      <c r="AF1" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="AE1" s="35" t="s">
+      <c r="AG1" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="AF1" s="36" t="s">
+      <c r="AH1" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="AG1" s="36" t="s">
+      <c r="AI1" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="AH1" s="35" t="s">
+      <c r="AJ1" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="AI1" s="37" t="s">
+      <c r="AK1" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="AJ1" s="38" t="s">
+      <c r="AL1" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="AK1" s="37" t="s">
+      <c r="AM1" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="AL1" s="38" t="s">
+      <c r="AN1" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="AM1" s="39" t="s">
+      <c r="AO1" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="AN1" s="40" t="s">
+      <c r="AP1" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="AO1" s="40" t="s">
+      <c r="AQ1" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="AP1" s="40" t="s">
+      <c r="AR1" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="AQ1" s="41" t="s">
+      <c r="AS1" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="AR1" s="41" t="s">
+      <c r="AT1" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="AS1" s="41" t="s">
+      <c r="AU1" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="AT1" s="41" t="s">
+      <c r="AV1" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="AU1" s="42" t="s">
+      <c r="AW1" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="AV1" s="43" t="s">
+      <c r="AX1" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="AW1" s="43" t="s">
+      <c r="AY1" s="43" t="s">
         <v>216</v>
       </c>
-      <c r="AX1" s="43" t="s">
+      <c r="AZ1" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="AY1" s="12" t="s">
+      <c r="BA1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="AZ1" s="34" t="s">
+      <c r="BB1" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="BA1" s="44" t="s">
+      <c r="BC1" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="BB1" s="12" t="s">
+      <c r="BD1" s="12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>115</v>
       </c>
       <c r="B2" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="9">
         <v>365</v>
       </c>
-      <c r="D2" s="9">
+      <c r="F2" s="9">
         <v>400</v>
       </c>
-      <c r="E2" s="9">
+      <c r="G2" s="9">
         <v>0.02</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="H2" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="I2" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="46">
+      <c r="J2" s="46">
         <v>172</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="K2" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>0.35</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>0.7</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>278</v>
       </c>
-      <c r="N2" s="46" t="s">
+      <c r="P2" s="46" t="s">
         <v>220</v>
       </c>
-      <c r="O2" s="18">
+      <c r="Q2" s="18">
         <v>0.9</v>
       </c>
-      <c r="P2" s="18">
+      <c r="R2" s="18">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q2" s="47">
+      <c r="S2" s="47">
         <v>0.9</v>
       </c>
-      <c r="R2" s="47">
+      <c r="T2" s="47">
         <v>0</v>
       </c>
-      <c r="S2" s="47">
+      <c r="U2" s="47">
         <f>24*21</f>
         <v>504</v>
       </c>
-      <c r="T2" s="47">
+      <c r="V2" s="47">
         <f>24*7*6</f>
         <v>1008</v>
       </c>
-      <c r="U2" s="48" t="s">
+      <c r="W2" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="V2" s="26">
+      <c r="X2" s="26">
         <v>3</v>
       </c>
-      <c r="W2" s="26">
+      <c r="Y2" s="26">
         <v>0</v>
       </c>
-      <c r="X2">
+      <c r="Z2">
         <v>90</v>
       </c>
-      <c r="Y2">
+      <c r="AA2">
         <v>400</v>
       </c>
-      <c r="Z2" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="10">
+      <c r="AB2" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="10">
         <v>0</v>
       </c>
-      <c r="AB2" s="10">
+      <c r="AD2" s="10">
         <v>182.5</v>
       </c>
-      <c r="AC2" s="10">
+      <c r="AE2" s="10">
         <v>0.21634999999999999</v>
       </c>
-      <c r="AD2" t="b">
+      <c r="AF2" t="b">
         <v>0</v>
       </c>
-      <c r="AE2" s="49">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="49">
+      <c r="AG2" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="49">
         <v>0</v>
       </c>
-      <c r="AG2" s="49">
+      <c r="AI2" s="49">
         <v>182.5</v>
       </c>
-      <c r="AH2" s="49">
+      <c r="AJ2" s="49">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AI2" s="8">
-        <v>1</v>
-      </c>
-      <c r="AJ2" s="8">
+      <c r="AK2" s="8">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="8">
         <v>0</v>
       </c>
-      <c r="AK2" s="8">
+      <c r="AM2" s="8">
         <v>182.5</v>
       </c>
-      <c r="AL2" s="8">
+      <c r="AN2" s="8">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AM2" s="50">
-        <v>1</v>
-      </c>
-      <c r="AN2" s="50">
+      <c r="AO2" s="50">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="50">
         <v>0</v>
       </c>
-      <c r="AO2" s="50">
+      <c r="AQ2" s="50">
         <v>121.66670000000001</v>
       </c>
-      <c r="AP2" s="50">
+      <c r="AR2" s="50">
         <v>2.6738E-3</v>
       </c>
-      <c r="AQ2" s="51">
-        <v>1</v>
-      </c>
-      <c r="AR2" s="51">
+      <c r="AS2" s="51">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="51">
         <v>0</v>
       </c>
-      <c r="AS2" s="51">
+      <c r="AU2" s="51">
         <v>182.5</v>
       </c>
-      <c r="AT2" s="51">
+      <c r="AV2" s="51">
         <v>0.11268</v>
       </c>
-      <c r="AU2" s="11">
-        <v>1</v>
-      </c>
-      <c r="AV2" s="11">
+      <c r="AW2" s="11">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="11">
         <v>0</v>
       </c>
-      <c r="AW2" s="11">
+      <c r="AY2" s="11">
         <v>121.66670000000001</v>
       </c>
-      <c r="AX2" s="11">
+      <c r="AZ2" s="11">
         <v>2.7855000000000002E-3</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>219</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>257</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>257</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>115</v>
       </c>
       <c r="B3" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E3" s="9">
         <v>365</v>
       </c>
-      <c r="D3" s="9">
+      <c r="F3" s="9">
         <v>400</v>
       </c>
-      <c r="E3" s="9">
+      <c r="G3" s="9">
         <v>0.02</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="H3" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="I3" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="46">
+      <c r="J3" s="46">
         <v>30</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="K3" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>0.35</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>0.7</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>278</v>
       </c>
-      <c r="N3" s="46" t="s">
+      <c r="P3" s="46" t="s">
         <v>220</v>
       </c>
-      <c r="O3" s="18">
+      <c r="Q3" s="18">
         <v>0.9</v>
       </c>
-      <c r="P3" s="18">
+      <c r="R3" s="18">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q3" s="47">
+      <c r="S3" s="47">
         <v>0.9</v>
       </c>
-      <c r="R3" s="47">
+      <c r="T3" s="47">
         <v>0</v>
       </c>
-      <c r="S3" s="47">
+      <c r="U3" s="47">
         <f>24*21</f>
         <v>504</v>
       </c>
-      <c r="T3" s="47">
+      <c r="V3" s="47">
         <f>24*7*6</f>
         <v>1008</v>
       </c>
-      <c r="U3" s="48" t="s">
+      <c r="W3" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="V3" s="26">
+      <c r="X3" s="26">
         <v>3</v>
       </c>
-      <c r="W3" s="26">
+      <c r="Y3" s="26">
         <v>0</v>
       </c>
-      <c r="X3">
+      <c r="Z3">
         <v>90</v>
       </c>
-      <c r="Y3">
+      <c r="AA3">
         <v>400</v>
       </c>
-      <c r="Z3" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="10">
+      <c r="AB3" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="10">
         <v>0</v>
       </c>
-      <c r="AB3" s="10">
+      <c r="AD3" s="10">
         <v>182.5</v>
       </c>
-      <c r="AC3" s="10">
+      <c r="AE3" s="10">
         <v>0.21634999999999999</v>
       </c>
-      <c r="AD3" t="b">
+      <c r="AF3" t="b">
         <v>0</v>
       </c>
-      <c r="AE3" s="49">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="49">
+      <c r="AG3" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="49">
         <v>0</v>
       </c>
-      <c r="AG3" s="49">
+      <c r="AI3" s="49">
         <v>182.5</v>
       </c>
-      <c r="AH3" s="49">
+      <c r="AJ3" s="49">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AI3" s="8">
-        <v>1</v>
-      </c>
-      <c r="AJ3" s="8">
+      <c r="AK3" s="8">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="8">
         <v>0</v>
       </c>
-      <c r="AK3" s="8">
+      <c r="AM3" s="8">
         <v>182.5</v>
       </c>
-      <c r="AL3" s="8">
+      <c r="AN3" s="8">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AM3" s="50">
-        <v>1</v>
-      </c>
-      <c r="AN3" s="50">
+      <c r="AO3" s="50">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="50">
         <v>0</v>
       </c>
-      <c r="AO3" s="50">
+      <c r="AQ3" s="50">
         <v>121.66670000000001</v>
       </c>
-      <c r="AP3" s="50">
+      <c r="AR3" s="50">
         <v>2.6738E-3</v>
       </c>
-      <c r="AQ3" s="51">
-        <v>1</v>
-      </c>
-      <c r="AR3" s="51">
+      <c r="AS3" s="51">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="51">
         <v>0</v>
       </c>
-      <c r="AS3" s="51">
+      <c r="AU3" s="51">
         <v>182.5</v>
       </c>
-      <c r="AT3" s="51">
+      <c r="AV3" s="51">
         <v>0.11268</v>
       </c>
-      <c r="AU3" s="11">
-        <v>1</v>
-      </c>
-      <c r="AV3" s="11">
+      <c r="AW3" s="11">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="11">
         <v>0</v>
       </c>
-      <c r="AW3" s="11">
+      <c r="AY3" s="11">
         <v>121.66670000000001</v>
       </c>
-      <c r="AX3" s="11">
+      <c r="AZ3" s="11">
         <v>2.7855000000000002E-3</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="BA3" t="s">
         <v>219</v>
       </c>
-      <c r="AZ3" t="s">
+      <c r="BB3" t="s">
         <v>257</v>
       </c>
-      <c r="BA3" t="s">
+      <c r="BC3" t="s">
         <v>257</v>
       </c>
-      <c r="BB3" t="s">
+      <c r="BD3" t="s">
         <v>282</v>
       </c>
     </row>
